--- a/simple_game_test/user_total_rounds.xlsx
+++ b/simple_game_test/user_total_rounds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D141"/>
+  <dimension ref="A1:D173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3172,6 +3172,580 @@
         <v>1</v>
       </c>
     </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>258</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr"/>
+      <c r="C142" t="inlineStr"/>
+      <c r="D142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>259</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>261</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>262</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>284</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>285</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>286</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>286</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>287</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr"/>
+      <c r="C152" t="inlineStr"/>
+      <c r="D152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>289</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr"/>
+      <c r="C153" t="inlineStr"/>
+      <c r="D153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>290</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>290</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>292</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr"/>
+      <c r="C156" t="inlineStr"/>
+      <c r="D156" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>294</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>294</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>295</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>295</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="D160" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>296</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="D161" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>296</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="D162" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>297</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="D163" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>297</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="D164" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>298</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr"/>
+      <c r="C165" t="inlineStr"/>
+      <c r="D165" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>299</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="D166" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>299</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="D167" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="D168" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="D169" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>301</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="D170" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>301</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="D171" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>302</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr"/>
+      <c r="C172" t="inlineStr"/>
+      <c r="D172" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr"/>
+      <c r="D173" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
